--- a/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/gpt_gpt-5.6-sol_judge_medium__vs__kimi_kimi-k2.6_judge_high.xlsx
+++ b/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/gpt_gpt-5.6-sol_judge_medium__vs__kimi_kimi-k2.6_judge_high.xlsx
@@ -2039,33 +2039,35 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.00262499088421464</v>
+        <v>3264.78354097344</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007125025149434805</v>
+        <v>1433.61345800804</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2104,33 +2106,35 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>43166.37245903257</v>
+        <v>13985.71837501368</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03720901440829039</v>
+        <v>1385.209500032943</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2169,33 +2173,35 @@
       <c r="H4" t="b">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>20374.62725001387</v>
+        <v>13735.49320799066</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02745800884440541</v>
+        <v>1146.384915977251</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2234,33 +2240,35 @@
       <c r="H5" t="b">
         <v>1</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.007499998901039362</v>
+        <v>14137.08291697549</v>
       </c>
       <c r="M5" t="n">
-        <v>0.020249979570508</v>
+        <v>1936.015832994599</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2299,33 +2307,35 @@
       <c r="H6" t="b">
         <v>1</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>0.002082961145788431</v>
+        <v>7656.181333994027</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007166992872953415</v>
+        <v>2380.869124957826</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2364,33 +2374,35 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>44288.86158298701</v>
+        <v>14004.95737500023</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01287495251744986</v>
+        <v>1312.518708000425</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2429,33 +2441,35 @@
       <c r="H8" t="b">
         <v>1</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>28672.82058298588</v>
+        <v>12311.71470799018</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00925001222640276</v>
+        <v>1558.489874994848</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2494,33 +2508,35 @@
       <c r="H9" t="b">
         <v>1</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>28089.58487497875</v>
+        <v>13373.21162497392</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03812502836808562</v>
+        <v>1036.535708000883</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2559,33 +2575,35 @@
       <c r="H10" t="b">
         <v>1</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>0.00162498326972127</v>
+        <v>14751.39629200567</v>
       </c>
       <c r="M10" t="n">
-        <v>0.006291025783866644</v>
+        <v>1371.586332970764</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2624,33 +2642,35 @@
       <c r="H11" t="b">
         <v>1</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>27106.9604580407</v>
+        <v>11657.07462496357</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0220410292968154</v>
+        <v>1109.171874995809</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2689,33 +2709,35 @@
       <c r="H12" t="b">
         <v>1</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>27752.08399997791</v>
+        <v>13814.24845801666</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01208303729072213</v>
+        <v>1933.527458983008</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2754,33 +2776,35 @@
       <c r="H13" t="b">
         <v>1</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>0.00866700429469347</v>
+        <v>19330.70495800348</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0272089964710176</v>
+        <v>1257.220750034321</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2819,33 +2843,35 @@
       <c r="H14" t="b">
         <v>1</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>0.002917018719017506</v>
+        <v>13652.784875012</v>
       </c>
       <c r="M14" t="n">
-        <v>0.009167008101940155</v>
+        <v>1097.669790964574</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2884,33 +2910,35 @@
       <c r="H15" t="b">
         <v>1</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>20977.36300004181</v>
+        <v>14269.99133295612</v>
       </c>
       <c r="M15" t="n">
-        <v>0.009374984074383974</v>
+        <v>1360.813042032532</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2949,33 +2977,35 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>0.002666027285158634</v>
+        <v>4728.253916022368</v>
       </c>
       <c r="M16" t="n">
-        <v>0.007790978997945786</v>
+        <v>1698.202166007832</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3014,33 +3044,35 @@
       <c r="H17" t="b">
         <v>1</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>18387.56654202007</v>
+        <v>13635.93795901397</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01195800723508</v>
+        <v>1968.724916980136</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3079,33 +3111,35 @@
       <c r="H18" t="b">
         <v>1</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>19925.72208296042</v>
+        <v>13023.47991697025</v>
       </c>
       <c r="M18" t="n">
-        <v>0.03750005271285772</v>
+        <v>2442.835042020306</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
